--- a/external/config/events.xlsx
+++ b/external/config/events.xlsx
@@ -1,127 +1,49 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Program\Slay The Robot_test\Slay-The-Robot\external\config\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D45AF11-71AE-452E-904A-9DD179893718}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Events" sheetId="1" r:id="rId1"/>
+    <sheet name="Events" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
-  <si>
-    <t>object_id</t>
-  </si>
-  <si>
-    <t>event_dialogue_object_id</t>
-  </si>
-  <si>
-    <t>event_background_texture_path</t>
-  </si>
-  <si>
-    <t>event_enemy_placement_is_automatic</t>
-  </si>
-  <si>
-    <t>event_enemy_placement_positions</t>
-  </si>
-  <si>
-    <t>event_weighted_enemy_object_ids</t>
-  </si>
-  <si>
-    <t>location_event_pool_validator_failed_strategy</t>
-  </si>
-  <si>
-    <t># 说明行（此行会被自动跳过）</t>
-  </si>
-  <si>
-    <t>在下方添加你的事件数据</t>
-  </si>
-  <si>
-    <t>event_act_1_boss_1</t>
-  </si>
-  <si>
-    <t>0,0|180,0|360,0</t>
-  </si>
-  <si>
-    <t>enemy_act_1_boss_1:1</t>
-  </si>
-  <si>
-    <t>event_act_1_easy_combat_1</t>
-  </si>
-  <si>
-    <t>0,-40|0,40</t>
-  </si>
-  <si>
-    <t>enemy_1:1,enemy_2:1,enemy_3:1|enemy_1:1,enemy_2:1,enemy_3:1|enemy_1:1,enemy_2:1,enemy_3:1</t>
-  </si>
-  <si>
-    <t>event_pick_something</t>
-  </si>
-  <si>
-    <t>dialogue_pick_something</t>
-  </si>
-  <si>
-    <t>enemy_1:1,enemy_2:1|enemy_2:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">event_enemy_placement_positions格式: x,y|x,y (多位置用|分隔) | </t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>event_weighted_enemy_object_ids格式: enemy_id:weight,enemy_id:weight|enemy_id:weight (多组用|分隔)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="134"/>
+      <b val="1"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF2E8B57"/>
-        <bgColor rgb="FF2E8B57"/>
+        <fgColor rgb="002E8B57"/>
+        <bgColor rgb="002E8B57"/>
       </patternFill>
     </fill>
   </fills>
@@ -134,46 +56,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -461,112 +430,311 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="27" style="2" customWidth="1"/>
-    <col min="2" max="2" width="26" style="2" customWidth="1"/>
-    <col min="3" max="3" width="50" style="2" customWidth="1"/>
-    <col min="4" max="4" width="36" style="2" customWidth="1"/>
-    <col min="5" max="5" width="33" style="2" customWidth="1"/>
-    <col min="6" max="6" width="50" style="2" customWidth="1"/>
-    <col min="7" max="7" width="47" style="2" customWidth="1"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="33" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="47" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>object_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>event_dialogue_object_id</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>event_background_texture_path</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>event_enemy_placement_is_automatic</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>event_enemy_placement_positions</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>event_weighted_enemy_object_ids</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>location_event_pool_validator_failed_strategy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t># 说明行（此行会被自动跳过）</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>在下方添加你的事件数据</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>event_enemy_placement_positions格式: x,y|x,y (多位置用|分隔) | event_weighted_enemy_object_ids格式: enemy_id:weight,enemy_id:weight|enemy_id:weight (多组用|分隔)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>event_act_1_boss_1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="b">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="42" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="28" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G5" s="2">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.0,0.0|180.0,0.0|360.0,0.0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>enemy_act_1_boss_1:1.0</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>event_act_1_easy_combat_1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0.0,-40.0|0.0,40.0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>enemy_1:1.0,enemy_2:1.0,enemy_3:1.0|enemy_1:1.0,enemy_2:1.0,enemy_3:1.0|enemy_1:1.0,enemy_2:1.0,enemy_3:1.0</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>event_act_1_easy_combat_2</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0.0,-40.0|0.0,40.0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>enemy_3:1.0</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>event_act_1_easy_combat_3</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.0,-40.0|0.0,40.0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>enemy_1:1.0|enemy_2:1.0</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>event_act_1_easy_combat_4</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0.0,-40.0|0.0,40.0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>enemy_4:1.0</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>event_act_1_miniboss_1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0.0,-40.0|0.0,40.0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>enemy_act_1_miniboss_1:1.0</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>event_act_1_miniboss_2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0.0,-40.0|0.0,40.0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>enemy_act_1_miniboss_2:1.0|enemy_act_1_miniboss_2:1.0</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>event_act_1_miniboss_3</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0.0,-40.0|0.0,40.0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>enemy_act_1_miniboss_1:1.0</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>event_pick_something</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>dialogue_pick_something</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0.0,-40.0|0.0,40.0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>enemy_1:1.0,enemy_2:1.0|enemy_2:1.0</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/external/config/events.xlsx
+++ b/external/config/events.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Events" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Events" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:X11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -445,6 +445,23 @@
     <col width="33" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
     <col width="47" customWidth="1" min="7" max="7"/>
+    <col width="49" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="9" max="9"/>
+    <col width="36" customWidth="1" min="10" max="10"/>
+    <col width="35" customWidth="1" min="11" max="11"/>
+    <col width="50" customWidth="1" min="12" max="12"/>
+    <col width="50" customWidth="1" min="13" max="13"/>
+    <col width="48" customWidth="1" min="14" max="14"/>
+    <col width="50" customWidth="1" min="15" max="15"/>
+    <col width="50" customWidth="1" min="16" max="16"/>
+    <col width="50" customWidth="1" min="17" max="17"/>
+    <col width="35" customWidth="1" min="18" max="18"/>
+    <col width="50" customWidth="1" min="19" max="19"/>
+    <col width="50" customWidth="1" min="20" max="20"/>
+    <col width="48" customWidth="1" min="21" max="21"/>
+    <col width="50" customWidth="1" min="22" max="22"/>
+    <col width="50" customWidth="1" min="23" max="23"/>
+    <col width="50" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -483,6 +500,91 @@
           <t>location_event_pool_validator_failed_strategy</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>event_dialogue_initial_dialogue_state_object_id</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>event_dialogue_state_dialogue_texture_path</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>event_dialogue_state_prompt_bbcode</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>event_dialogue_option_1_object_id</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>event_dialogue_option_1_bbcode</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>event_dialogue_option_1_failed_validator_bbcode</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>event_dialogue_option_1_next_dialogue_state_id</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>event_dialogue_option_1_visible_on_failed_validation</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>event_dialogue_option_1_actions_json</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>event_dialogue_option_1_validators_json</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>event_dialogue_option_2_object_id</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>event_dialogue_option_2_bbcode</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>event_dialogue_option_2_failed_validator_bbcode</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>event_dialogue_option_2_next_dialogue_state_id</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>event_dialogue_option_2_visible_on_failed_validation</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>event_dialogue_option_2_actions_json</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>event_dialogue_option_2_validators_json</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -500,10 +602,6 @@
           <t>event_enemy_placement_positions格式: x,y|x,y (多位置用|分隔) | event_weighted_enemy_object_ids格式: enemy_id:weight,enemy_id:weight|enemy_id:weight (多组用|分隔)</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -511,8 +609,6 @@
           <t>event_act_1_boss_1</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="b">
         <v>0</v>
       </c>
@@ -536,8 +632,6 @@
           <t>event_act_1_easy_combat_1</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="b">
         <v>1</v>
       </c>
@@ -561,8 +655,6 @@
           <t>event_act_1_easy_combat_2</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="b">
         <v>1</v>
       </c>
@@ -586,8 +678,6 @@
           <t>event_act_1_easy_combat_3</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="b">
         <v>1</v>
       </c>
@@ -611,8 +701,6 @@
           <t>event_act_1_easy_combat_4</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="b">
         <v>1</v>
       </c>
@@ -636,8 +724,6 @@
           <t>event_act_1_miniboss_1</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="b">
         <v>1</v>
       </c>
@@ -661,8 +747,6 @@
           <t>event_act_1_miniboss_2</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
       <c r="D9" t="b">
         <v>1</v>
       </c>
@@ -686,8 +770,6 @@
           <t>event_act_1_miniboss_3</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" t="b">
         <v>1</v>
       </c>
@@ -716,7 +798,6 @@
           <t>dialogue_pick_something</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="b">
         <v>1</v>
       </c>
@@ -732,6 +813,77 @@
       </c>
       <c r="G11" t="n">
         <v>1</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>dialogue_state_pick_something_initial</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>external/sprites/events/event_pick_something.png</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>测试事件。请选择一个选项...</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>dialogue_pick_something_option_1</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>[color=red]失去10点生命[/color] 并 [color=green]获得100金币[/color]</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>[color=grey][锁定]：生命不足[/color]</t>
+        </is>
+      </c>
+      <c r="O11" t="b">
+        <v>1</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>[{"res://scripts/actions/ActionAddHealth.gd": {"health_amount": -10}}, {"res://scripts/actions/player_actions/ActionAddMoney.gd": {"money_amount": 100}}]</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>[{"res://scripts/validators/ValidatorPlayerHealth.gd": {"health_amount": 11}}]</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>dialogue_pick_something_option_2</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>[color=red]失去50金币[/color] 并 [color=green]获得随机稀有卡牌[/color]</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>[color=grey][锁定]：金币不足[/color]</t>
+        </is>
+      </c>
+      <c r="V11" t="b">
+        <v>1</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>[{"res://scripts/actions/pick_card_actions/ActionPickCards.gd": {"action_data": [{"res://scripts/actions/cardset_actions/ActionAddCardsToDeck.gd": {}}], "card_pick_type": 8, "draft_from_card_pool": true, "draft_is_weighted": false, "draft_max_card_amount": 1, "draft_use_pity_system": false, "draft_use_player_draft": false, "max_card_amount": 1, "min_card_amount": 1, "pick_draft_cards": false, "random_selection": true, "rng_name": "rng_events", "validator_data": [{"res://scripts/validators/card/ValidatorCardRarity.gd": {"card_rarities": [3]}}, {"res://scripts/validators/card/ValidatorCardDraftable.gd": {}}]}}, {"res://scripts/actions/player_actions/ActionAddMoney.gd": {"money_amount": -50}}]</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>[{"res://scripts/validators/ValidatorMoney.gd": {"money_amount": 50}}]</t>
+        </is>
       </c>
     </row>
   </sheetData>
